--- a/assets/constructions/examples/ctd_thi.xlsx
+++ b/assets/constructions/examples/ctd_thi.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP6"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,26 +639,46 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S32U MSKN L 12-K</t>
+          <t>H25R-MTFNL16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>MTFNR/L</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MSKNL</t>
+          <t>MTFNL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -672,14 +692,14 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>-1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SN1204H</t>
+          <t>TN1604H</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -689,40 +709,36 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SNMG120408</t>
+          <t>TN..1604..</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ISO_5609:32</t>
+          <t>ISO_5609:25</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ISO_SN1204H</t>
+          <t>ISO_TN1604H</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="P2" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>32USKNL12</t>
+          <t>25RTFNL16</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>ZX</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -731,12 +747,10 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="b">
-        <v>0</v>
-      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
@@ -747,28 +761,22 @@
       <c r="AB2" t="b">
         <v>0</v>
       </c>
-      <c r="AC2" t="n">
-        <v>30</v>
-      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="AG2" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-11</v>
-      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
@@ -780,37 +788,41 @@
           <t>STL</t>
         </is>
       </c>
-      <c r="AN2" t="n">
-        <v>2.05</v>
-      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2020 / PALBIT основной каталог EN</t>
-        </is>
-      </c>
+          <t>2017/derek Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A20Q SVUC R 11</t>
+          <t>S16N-SCKCL09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>SCK*R/L</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SVUCR</t>
+          <t>SCKCL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -824,14 +836,14 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="H3" t="n">
-        <v>-3</v>
+        <v>15</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VC1103H</t>
+          <t>CC09T3H</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,86 +853,74 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>VCMT110304</t>
+          <t>CC..09T3..</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ISO_5609:20</t>
+          <t>ISO_5609:16</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ISO_VC1103H</t>
+          <t>ISO_CC09T3H</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>20QVUCR11</t>
+          <t>16NCKCL09</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ZXA</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="b">
-        <v>0</v>
-      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="b">
         <v>0</v>
       </c>
-      <c r="AC3" t="n">
-        <v>18</v>
-      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AG3" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-5</v>
-      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
@@ -932,17 +932,21 @@
           <t>STL</t>
         </is>
       </c>
-      <c r="AN3" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2020 / PALBIT основной каталог EN</t>
-        </is>
-      </c>
+          <t>2017/derek Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -952,7 +956,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S25T SDUC L 11-BT</t>
+          <t>A25R PCLN L 12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -962,7 +966,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SDUCL-BT</t>
+          <t>PCLNL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -972,18 +976,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H4" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DC11T3H</t>
+          <t>CN1204H</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -993,7 +997,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>DCMT11T304</t>
+          <t>CNMG120408</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1003,7 +1007,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ISO_DC11T3H</t>
+          <t>ISO_CN1204H</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1021,12 +1025,12 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>25TDUCL11-BT</t>
+          <t>25RCLNL12</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>ZX</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1035,17 +1039,17 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="b">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="b">
@@ -1061,17 +1065,17 @@
         <v>17</v>
       </c>
       <c r="AF4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AG4" t="n">
         <v>40</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-6</v>
+        <v>-13.5</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
@@ -1094,27 +1098,41 @@
         <is>
           <t>2020 / PALBIT основной каталог EN</t>
         </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>370.82</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>34090.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A12M-SCKPL08</t>
+          <t>A32S PDUN L 15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SCK*R/L</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SCKPL</t>
+          <t>PDUNL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1124,18 +1142,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>-3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CP0802H</t>
+          <t>DN1506H</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1145,36 +1163,40 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>CP..0802..</t>
+          <t>DNMG150608</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ISO_5609:12</t>
+          <t>ISO_5609:32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ISO_CP0802H</t>
+          <t>ISO_DN1506H</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="P5" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>12MCKPL08</t>
+          <t>32SDUNL15</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>ZXA</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1183,10 +1205,12 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
@@ -1195,24 +1219,30 @@
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>30</v>
+      </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AE5" t="n">
-        <v>7.5</v>
+        <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-14</v>
+      </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1224,14 +1254,30 @@
           <t>STL</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr"/>
+      <c r="AN5" t="n">
+        <v>1.4</v>
+      </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2017/derek Металлорежущий инструмент и оснастка</t>
-        </is>
+          <t>2020 / PALBIT основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>434.01</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>39900.15</v>
       </c>
     </row>
     <row r="6">
@@ -1242,13 +1288,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A08H-SCLCR06</t>
+          <t>A12K-SDQCR07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SCLCR</t>
+          <t>SDQCR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1262,14 +1308,14 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>95</v>
+        <v>107.5</v>
       </c>
       <c r="H6" t="n">
-        <v>-5</v>
+        <v>-17.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CC0602H</t>
+          <t>DC0702H</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1279,25 +1325,25 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>CC..0602..</t>
+          <t>DC..0702..</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ISO_5609:8</t>
+          <t>ISO_5609:12</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ISO_CC0602H</t>
+          <t>ISO_DC0702H</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1307,12 +1353,12 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>08HCLCR06</t>
+          <t>12KDQCR07</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ZX</t>
+          <t>ZXA</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1339,16 +1385,16 @@
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="AG6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
@@ -1373,6 +1419,12 @@
           <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
+      <c r="AQ6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
